--- a/Week 5/excel_analogy_PK_FK.xlsx
+++ b/Week 5/excel_analogy_PK_FK.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\Instructor_material\wk5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab76ec252c957cd7/Desktop/data_bootcamp_folder/instructor_ref/instructor_ref/Week 5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06F721F7-440D-4DF2-96B3-EDBBAA1ECA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{06F721F7-440D-4DF2-96B3-EDBBAA1ECA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9861989C-0A5C-4158-8B8C-C85EEED5C969}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0701A39-01C2-4DF2-9B45-E2CE2A8F3DB2}"/>
+    <workbookView xWindow="1510" yWindow="850" windowWidth="21330" windowHeight="12620" activeTab="1" xr2:uid="{C0701A39-01C2-4DF2-9B45-E2CE2A8F3DB2}"/>
   </bookViews>
   <sheets>
     <sheet name="customer" sheetId="1" r:id="rId1"/>
@@ -536,12 +536,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB5DE71-0CFC-4298-91DA-52AF9A2DC312}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -636,15 +636,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43190AF-4965-45E6-8650-0B2D8CC453FF}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.2" thickBot="1">
+    <row r="1" spans="1:6" ht="28.5" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
